--- a/Backend/sample_data/data_dummy_staff.xlsx
+++ b/Backend/sample_data/data_dummy_staff.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Maya Putri</t>
+          <t>Nadia Lestari</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>maya.putri@example.com</t>
+          <t>nadia.lestari@example.com</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Danu Pratama</t>
+          <t>Rafi Hidayat</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>danu.pratama@example.com</t>
+          <t>rafi.hidayat@example.com</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
